--- a/needs-a-push-2026-09-27.xlsx
+++ b/needs-a-push-2026-09-27.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs a Push" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Needs a Push'!$A$1:$M$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Needs a Push'!$A$1:$M$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -518,37 +518,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>31988</t>
+          <t>47934</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Light Brown Pinstripe Pumpkin Smocked Dress and Bloomer Set</t>
+          <t>Sage Green Puppy Dog Petal Smocked Dress</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>4LC26Q33</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>FW26 New Fall</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46230</v>
+        <v>46276</v>
       </c>
       <c r="G2" t="n">
-        <v>67</v>
+        <v>247</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.2548</v>
+        <v>0.0039</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -563,106 +563,106 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>31990</t>
+          <t>47935</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Light Blue Pumpkin Vine Smocked Dress and Bloomers</t>
+          <t>Sage Green Puppy Dog Petal Smocked Romper</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>4LC26Q33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>FW26 New Fall</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46230</v>
+        <v>46276</v>
       </c>
       <c r="G3" t="n">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.3202</v>
+        <v>0.013</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.0351</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>36366</t>
+          <t>47936</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Light Blue Crosses Smocked Overalls</t>
+          <t>Golden Wheat Pumpkin Collared Dress</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Stage 2</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>4LC26Q33</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>FW26 New Fall</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46230</v>
+        <v>46276</v>
       </c>
       <c r="G4" t="n">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -677,103 +677,103 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>36368</t>
+          <t>47937</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sage Green Construction Smocked Overalls</t>
+          <t>Golden Wheat Pumpkin Smocked Petal Collar Dress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>4LC26Q33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>FW26 New Fall</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46230</v>
+        <v>46276</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.2162</v>
+        <v>0.0078</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.1875</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>47938</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Light Blue Golf Hole Shirt</t>
+          <t>Golden Wheat Pumpkin Smocked Petal Collar Romper</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stage 3</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>4LC26Q33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>FW26 New Fall</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46230</v>
+        <v>46276</v>
       </c>
       <c r="G6" t="n">
-        <v>47</v>
+        <v>147</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
@@ -791,55 +791,55 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>33890</t>
+          <t>31807</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Light Blue Gingham Basic Baby Jon Jon</t>
+          <t>Red Christmas Plaid Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Stage 5</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46221</v>
+        <v>46266</v>
       </c>
       <c r="G7" t="n">
-        <v>266</v>
+        <v>312</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.225</v>
+        <v>0.0427</v>
       </c>
       <c r="I7" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.7531</v>
+        <v>0.2812</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -848,169 +848,169 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>31848</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Green Gingham Alligator Bubble Romper</t>
+          <t>Navy Blue Nativity Long Sleeve Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46221</v>
+        <v>46266</v>
       </c>
       <c r="G8" t="n">
-        <v>263</v>
+        <v>304</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.35</v>
+        <v>0.0152</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.1948</v>
+        <v>0.4</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>31851</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Light Blue Seersucker Ruffle Dress</t>
+          <t>Navy Blue Velvet Gold Nativity Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stage 2</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46221</v>
+        <v>46266</v>
       </c>
       <c r="G9" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>0.0381</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>31852</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>White and Blue Holy Smocked Overalls</t>
+          <t>Green Christmas Mistletoe Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Stage 2</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46221</v>
+        <v>46266</v>
       </c>
       <c r="G10" t="n">
-        <v>196</v>
+        <v>688</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.1708</v>
+        <v>0.0337</v>
       </c>
       <c r="I10" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1019,55 +1019,55 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>36532</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Blue Crosses Smocked JonJon</t>
+          <t>Red Velvet Christmas Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Stage 5</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>46221</v>
+        <v>46266</v>
       </c>
       <c r="G11" t="n">
-        <v>145</v>
+        <v>723</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0063</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.5625</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1076,55 +1076,55 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>38501</t>
+          <t>31903</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blue Puppy Golf Shirt</t>
+          <t>Navy Blue Santa Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Stage 3</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>46221</v>
+        <v>46266</v>
       </c>
       <c r="G12" t="n">
-        <v>238</v>
+        <v>370</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.1167</v>
+        <v>0.0123</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.4286</v>
+        <v>0.8571</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1133,112 +1133,112 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>38502</t>
+          <t>32059</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Green Tractor Golf Shirt</t>
+          <t>Red Poplin Santa Long Sleeve Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Stage 3</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>46221</v>
+        <v>46266</v>
       </c>
       <c r="G13" t="n">
-        <v>217</v>
+        <v>471</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.064</v>
+        <v>0.0057</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>70212</t>
+          <t>32126</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Perfect Onesie Unisex Collared Romper</t>
+          <t>Red &amp; White Santa Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>46221</v>
+        <v>46266</v>
       </c>
       <c r="G14" t="n">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.0692</v>
+        <v>0.0174</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.2222</v>
+        <v>0.875</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1247,121 +1247,121 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>48922</t>
+          <t>32223</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Grey Gingham Puppies in Truck Shortalls</t>
+          <t>Pink Christmas Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stage 5</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4LC26Q22</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Q2 restock</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>46211</v>
+        <v>46266</v>
       </c>
       <c r="G15" t="n">
-        <v>66</v>
+        <v>302</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.1053</v>
+        <v>0.0047</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>47894</t>
+          <t>32279</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Light Blue Pumpkin Applique Collared Dress</t>
+          <t>Light Blue Smocked Nativity Collared Dress</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4LC26Q32</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FW26-B&amp;C</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="G16" t="n">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.3599</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.009599999999999999</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1373,52 +1373,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>32501</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Light Blue Pumpkin Applique Overalls</t>
+          <t>Green Velvet Santa Smocked Dress</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4LC26Q32</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FW26-B&amp;C</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="G17" t="n">
-        <v>116</v>
+        <v>353</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.1429</v>
+        <v>0.0069</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.0303</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1430,37 +1430,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>38516</t>
+          <t>32502</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sage Green Apple Polo Golf Shirt</t>
+          <t>Light Blue Christmas Tree Smocked Knit Dress</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stage 2</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3LC26Q31</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FW26A BtS &amp; Halloween ReOrder</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>46188</v>
+        <v>46266</v>
       </c>
       <c r="G18" t="n">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.1533</v>
+        <v>0.0048</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Fall/Winter</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1487,290 +1487,7643 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>32089</t>
+          <t>32504</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pink Gingham Smocked Bishop Dress</t>
+          <t>Green Velvet Santa Smocked Dress and Bloomers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stage 3</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3LC26Q21</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Q2 Reorder</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>46168</v>
+        <v>46266</v>
       </c>
       <c r="G19" t="n">
-        <v>146</v>
+        <v>258</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.396</v>
+        <v>0.0074</v>
       </c>
       <c r="I19" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.5354</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>32572</t>
+          <t>32507</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pink and White bows Smocked Ruffle Romper</t>
+          <t>Light Blue Christmas Tree Smocked Knit Ruffle Romper</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Stage 3</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3LC26Q21</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Q2 Reorder</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>46168</v>
+        <v>46266</v>
       </c>
       <c r="G20" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.3143</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.0227</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>36366</t>
+          <t>32508</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Light Blue Crosses Smocked Overalls</t>
+          <t>Dark Blue Nativity Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Stage 2</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3LC26Q21</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Q2 Reorder</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>46168</v>
+        <v>46266</v>
       </c>
       <c r="G21" t="n">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.2722</v>
+        <v>0.0054</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.1633</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>32509</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Light Blue Golf Hole Shirt</t>
+          <t>Red Velvet Gold Nativity Smocked Dress</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Stage 3</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3LC26Q21</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Q2 Reorder</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>46168</v>
+        <v>46266</v>
       </c>
       <c r="G22" t="n">
-        <v>96</v>
+        <v>264</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.2882</v>
+        <v>0.0167</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.0408</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>32520</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Green Christmas Tree Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G23" t="n">
+        <v>148</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>32521</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Red Santa Sleigh Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G24" t="n">
+        <v>143</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>32524</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Red and Green Christmas Plaid Smocked Dress</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G25" t="n">
+        <v>170</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>32590</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pink Hearts &amp; Bows Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G26" t="n">
+        <v>285</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>33226</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Red Santa Smocked Ruffle Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G27" t="n">
+        <v>219</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>33227</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Red Santa Smocked Ruffle Romper</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G28" t="n">
+        <v>95</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>33228</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Blue Nativity Smocked Ruffle Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G29" t="n">
+        <v>201</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0.2143</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>33229</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Red Corduroy Mistletoe Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G30" t="n">
+        <v>385</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="I30" t="n">
+        <v>14</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>33230</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Green Corduroy Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G31" t="n">
+        <v>420</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>33231</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Blue Velvet Silver Bows Smocked Ruffle Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G32" t="n">
+        <v>319</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="I32" t="n">
+        <v>12</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>33232</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Green Velvet Christmas Tree Ruffle Dress</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G33" t="n">
+        <v>309</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33233</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Blue Nativity Smocked Ruffle Romper</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G34" t="n">
+        <v>103</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>33234</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Red Bishop Dress Christmas Bows Smocked Ruffle Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G35" t="n">
+        <v>310</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>33762</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Light Blue Nativity Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G36" t="n">
+        <v>143</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>33770</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Red Velvet Christmas Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G37" t="n">
+        <v>271</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>33913</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Red and White Santa Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G38" t="n">
+        <v>115</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>35316</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Dark Blue Nativity Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G39" t="n">
+        <v>133</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>35356</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Green Christmas Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G40" t="n">
+        <v>262</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>0.0262</v>
+      </c>
+      <c r="I40" t="n">
+        <v>11</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>35456</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Red Plaid Truck &amp; Tree Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G41" t="n">
+        <v>105</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>36340</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Navy Blue Santa Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G42" t="n">
+        <v>194</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>36378</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Red and Green Christmas Plaid Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G43" t="n">
+        <v>154</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>36379</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Green Corduroy Santa Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G44" t="n">
+        <v>349</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>36381</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Light Blue Nativity Overalls</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G45" t="n">
+        <v>113</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>36383</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Red Santa Sleigh Overalls</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G46" t="n">
+        <v>112</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>36507</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Red Santa Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G47" t="n">
+        <v>210</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>36508</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Blue Nativity Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G48" t="n">
+        <v>169</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>36509</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Red Corduroy Mistletoe Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G49" t="n">
+        <v>142</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>36520</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Green Corduroy Santa Dress Shirt</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G50" t="n">
+        <v>349</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>36522</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sand Beige Reindeer Dress Shirt</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G51" t="n">
+        <v>103</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>38075</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Beige Nativity Smocked Shirt and Blue Pants</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G52" t="n">
+        <v>114</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>38081</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Red Santa Smocked Shirt and Navy Pants Set</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G53" t="n">
+        <v>143</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>38111</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sand Beige Reindeer Shirt and Brown Pants Set</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G54" t="n">
+        <v>96</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>75720</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Red Christmas Tree Knit Cardigan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G55" t="n">
+        <v>128</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>75721</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Navy Blue Christmas Santa Knit Cardigan</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3LC26Q33</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>FW26 Ship C</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G56" t="n">
+        <v>144</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>61010</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Pink Sparkly Bow Sweater</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>6LC26Q32</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>FW26 Christmas</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G57" t="n">
+        <v>238</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>61013</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Red Sweater with Glitter Bow</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>6LC26Q32</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>FW26 Christmas</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G58" t="n">
+        <v>297</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>61014</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Red Santa Sweater</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>6LC26Q32</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>FW26 Christmas</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G59" t="n">
+        <v>242</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>61016</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Pink Reindeer Sweater</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>6LC26Q32</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>FW26 Christmas</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G60" t="n">
+        <v>203</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>61017</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Green Santa Christmas Sweater</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>6LC26Q32</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>FW26 Christmas</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G61" t="n">
+        <v>229</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>0.0895</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61018</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Blue Reindeer Christmas Sweater</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>6LC26Q32</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>FW26 Christmas</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G62" t="n">
+        <v>167</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>61023</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Blue Sparkly Bow Sweater</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>6LC26Q32</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>FW26 Christmas</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G63" t="n">
+        <v>301</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>61024</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cream Sparkly Bow Sweater</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>6LC26Q32</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>FW26 Christmas</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G64" t="n">
+        <v>300</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>33287</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sage Green Pumpkin Smocked Ruffle Dress</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G65" t="n">
+        <v>101</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>33288</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sage Green Pumpkin Smocked Ruffle Romper</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G66" t="n">
+        <v>71</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0.2467</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>33292</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Heritage Custom Rose Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G67" t="n">
+        <v>153</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0.1325</v>
+      </c>
+      <c r="I67" t="n">
+        <v>7</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>0.2121</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>33293</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Heritage Custom Rose Layered Ruffle Dress</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G68" t="n">
+        <v>206</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>33296</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Heritage Rose Ruffle Smocked Dress</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G69" t="n">
+        <v>230</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>33297</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Heritage Rose Ruffle Smocked Romper</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G70" t="n">
+        <v>130</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>33298</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Heritage Rose Ruffle Smocked Playsuit</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G71" t="n">
+        <v>131</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>33309</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Red and Cream Gingham Farm Smocked Dress</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G72" t="n">
+        <v>163</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>33310</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pistachio Green Mallard Duck Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G73" t="n">
+        <v>142</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="I73" t="n">
+        <v>5</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0.0617</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>36524</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Cream Pumpkin Dress Shirt</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G74" t="n">
+        <v>132</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>36546</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Heritage Blue Puppy Dog Overalls</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G75" t="n">
+        <v>141</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>36548</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sage Green Puppy Dog Overalls</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G76" t="n">
+        <v>106</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>36549</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Sage Green Pumpkin Smocked Jon-Jons</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G77" t="n">
+        <v>82</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="I77" t="n">
+        <v>7</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>36553</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Red and Cream Gingham Farm Overalls</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G78" t="n">
+        <v>70</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>36554</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pistachio Green Mallard Duck Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G79" t="n">
+        <v>81</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>38131</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Pistachio Green Mallard Duck Smocked Shirt and Shorts Set</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G80" t="n">
+        <v>124</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.0533</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>75731</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Heirloom Pink Roses Collared Sweater</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3LC26Q35</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>FW26- New Thankgiving</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G81" t="n">
+        <v>252</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>31888</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sage Green Turkey Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G82" t="n">
+        <v>352</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>0.1414</v>
+      </c>
+      <c r="I82" t="n">
+        <v>15</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>0.2174</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>31898</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Blue Pumpkin Gingham Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G83" t="n">
+        <v>254</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="I83" t="n">
+        <v>34</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>31899</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Sage Green Pumpkin Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G84" t="n">
+        <v>240</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="I84" t="n">
+        <v>80</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>0.4494</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>31900</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Cobalt Blue Turkey Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G85" t="n">
+        <v>263</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0.0605</v>
+      </c>
+      <c r="I85" t="n">
+        <v>15</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>31906</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Light Blue Puppy Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G86" t="n">
+        <v>200</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="I86" t="n">
+        <v>20</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>31907</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sage Green Mallard Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G87" t="n">
+        <v>317</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0.1795</v>
+      </c>
+      <c r="I87" t="n">
+        <v>23</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0.2674</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>31987</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Light Brown Smocked Ruffle Dress</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G88" t="n">
+        <v>159</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0.1589</v>
+      </c>
+      <c r="I88" t="n">
+        <v>9</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0.2195</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>31988</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Light Brown Pinstripe Pumpkin Smocked Dress and Bloomer Set</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G89" t="n">
+        <v>67</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>31990</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Light Blue Pumpkin Vine Smocked Dress and Bloomers</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G90" t="n">
+        <v>86</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="I90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>31994</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Blue and Pink Bow Smocked Romper</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G91" t="n">
+        <v>123</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="I91" t="n">
+        <v>2</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>32277</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Light Brown Gingham Pumpkin Vine Ruffle Dress</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G92" t="n">
+        <v>154</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0.1272</v>
+      </c>
+      <c r="I92" t="n">
+        <v>5</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0.1724</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>32278</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Light Blue Pumpkin Vine Smocked Dress</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G93" t="n">
+        <v>212</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="I93" t="n">
+        <v>6</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>0.1224</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>32597</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Brown Floral Tunic and Leggings Set</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G94" t="n">
+        <v>85</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>0.1149</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>32598</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Brown Floral Smocked. Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G95" t="n">
+        <v>78</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="I95" t="n">
+        <v>12</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>33053</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>White Cotton Heirloom Bloomers</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G96" t="n">
+        <v>73</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>33224</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Light Blue Gingham Smocked Dress</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G97" t="n">
+        <v>215</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>33225</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Light Brown Pumpkin Smocked Collared Dress</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G98" t="n">
+        <v>226</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>0.2332</v>
+      </c>
+      <c r="I98" t="n">
+        <v>26</v>
+      </c>
+      <c r="J98" s="3" t="n">
+        <v>0.5778</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>33761</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Sage Green Turkey Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G99" t="n">
+        <v>194</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>0.0968</v>
+      </c>
+      <c r="I99" t="n">
+        <v>5</v>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>0.2083</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>34726</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Blue Pinstripe Smocked Ruffle Collar Dress</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G100" t="n">
+        <v>175</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="I100" t="n">
+        <v>16</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>0.1345</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>36337</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Blue Pumpkin Overalls</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G101" t="n">
+        <v>86</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="I101" t="n">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>0.0789</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>36338</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Cobalt Blue Turkey Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G102" t="n">
+        <v>122</v>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="I102" t="n">
+        <v>6</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>36348</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Sage Green Mallard Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G103" t="n">
+        <v>104</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>0.2149</v>
+      </c>
+      <c r="I103" t="n">
+        <v>2</v>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>36360</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Light Brown Mallard Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G104" t="n">
+        <v>111</v>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>0.1066</v>
+      </c>
+      <c r="I104" t="n">
+        <v>3</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>36364</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Light Gray Mallard Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G105" t="n">
+        <v>129</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="3" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>36365</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Light Green Alligator Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G106" t="n">
+        <v>57</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I106" t="n">
+        <v>2</v>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>36366</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Light Blue Crosses Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G107" t="n">
+        <v>264</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>36368</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Sage Green Construction Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G108" t="n">
+        <v>80</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>0.2162</v>
+      </c>
+      <c r="I108" t="n">
+        <v>6</v>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>36374</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Light Brown Pinstripe Pumpkin Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G109" t="n">
+        <v>90</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="I109" t="n">
+        <v>11</v>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>0.2075</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>36395</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Light Blue Pinstripe Turkey Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G110" t="n">
+        <v>87</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>0.1164</v>
+      </c>
+      <c r="I110" t="n">
+        <v>2</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>36501</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Blue Pinstripe Mallard Duck Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G111" t="n">
+        <v>196</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="I111" t="n">
+        <v>19</v>
+      </c>
+      <c r="J111" s="3" t="n">
+        <v>0.1939</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>36502</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Blue Gingham Train Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G112" t="n">
+        <v>100</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="I112" t="n">
+        <v>18</v>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>0.4737</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>36506</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Brown Turkey Face Overalls</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G113" t="n">
+        <v>203</v>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>0.0798</v>
+      </c>
+      <c r="I113" t="n">
+        <v>2</v>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>38074</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Light Brown Turkey Shirt and Sage Green Pants Set</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G114" t="n">
+        <v>140</v>
+      </c>
+      <c r="H114" s="3" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="I114" t="n">
+        <v>5</v>
+      </c>
+      <c r="J114" s="3" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>38091</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Light Gray Mallard Smocked Shirt and Pants</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G115" t="n">
+        <v>100</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>0.07870000000000001</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>38097</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>White Football Truck Shirt and Brown Pants Set</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G116" t="n">
+        <v>62</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>38504</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Light Blue Golf Hole Shirt</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G117" t="n">
+        <v>47</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>38505</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Sage Green Mallard Polo Shirt</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G118" t="n">
+        <v>90</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="I118" t="n">
+        <v>2</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>38517</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Brown Turkey Face T-Shirt</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G119" t="n">
+        <v>146</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>38518</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Sand Beige Pumpkin Tractor Polo Golf Shirt</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G120" t="n">
+        <v>70</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="I120" t="n">
+        <v>3</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>70214</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>White Lace Collared Girls Long Sleeve Bodysuit Romper</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G121" t="n">
+        <v>66</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>0.0743</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>70226</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>White Pointed Collar Button Romper</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>3LC26Q32</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>FW26-B (Fall)</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G122" t="n">
+        <v>84</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>0.06569999999999999</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>33890</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Light Blue Gingham Basic Baby Jon Jon</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Stage 5</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3LC26Q23</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Q2 ReOrder</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="G123" t="n">
+        <v>266</v>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="I123" t="n">
+        <v>61</v>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>0.7531</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>34343</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Green Gingham Alligator Bubble Romper</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3LC26Q23</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Q2 ReOrder</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="G124" t="n">
+        <v>263</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I124" t="n">
+        <v>30</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>0.1948</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>35199</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Light Blue Seersucker Ruffle Dress</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3LC26Q23</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Q2 ReOrder</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="G125" t="n">
+        <v>166</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>36386</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>White and Blue Holy Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>3LC26Q23</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Q2 ReOrder</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="G126" t="n">
+        <v>196</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>0.1708</v>
+      </c>
+      <c r="I126" t="n">
+        <v>33</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>0.8048999999999999</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>36532</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Blue Crosses Smocked JonJon</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Stage 5</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>3LC26Q23</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Q2 ReOrder</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="G127" t="n">
+        <v>145</v>
+      </c>
+      <c r="H127" s="3" t="n">
+        <v>0.08890000000000001</v>
+      </c>
+      <c r="I127" t="n">
+        <v>9</v>
+      </c>
+      <c r="J127" s="3" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>38501</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Blue Puppy Golf Shirt</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3LC26Q23</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Q2 ReOrder</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="G128" t="n">
+        <v>238</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>0.1167</v>
+      </c>
+      <c r="I128" t="n">
+        <v>12</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>38502</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Green Tractor Golf Shirt</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>3LC26Q23</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Q2 ReOrder</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="G129" t="n">
+        <v>217</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="I129" t="n">
+        <v>2</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>70212</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>The Perfect Onesie Unisex Collared Romper</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3LC26Q23</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Q2 ReOrder</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="G130" t="n">
+        <v>349</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="I130" t="n">
+        <v>6</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>33281</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Pink Gingham ABC School Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3LC26Q34</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Q3 New BtS &amp; Halloween</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G131" t="n">
+        <v>206</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I131" t="n">
+        <v>6</v>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>33282</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Blue Smocked Knit ABC School Dress</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3LC26Q34</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Q3 New BtS &amp; Halloween</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G132" t="n">
+        <v>204</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>0.1208</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>33283</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Pink and Orange GIngham Boo Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3LC26Q34</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Q3 New BtS &amp; Halloween</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G133" t="n">
+        <v>193</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>0.1458</v>
+      </c>
+      <c r="I133" t="n">
+        <v>2</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>0.0571</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Halloween</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>33284</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Pink and Orange Gingham Boo Smocked Dress and Bloomer Set</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3LC26Q34</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Q3 New BtS &amp; Halloween</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G134" t="n">
+        <v>90</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" s="3" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Halloween</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>36545</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Gray Boo Applique Overalls</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>3LC26Q34</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Q3 New BtS &amp; Halloween</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G135" t="n">
+        <v>94</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>0.1417</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Halloween</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>38125</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Blue Smocked ABC School Shirt and Shorts Set</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>3LC26Q34</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Q3 New BtS &amp; Halloween</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G136" t="n">
+        <v>107</v>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>38126</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Blue ABC School Shirt and Shorts Set</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>3LC26Q34</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Q3 New BtS &amp; Halloween</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G137" t="n">
+        <v>110</v>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>0.1167</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" s="3" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>38127</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Gray Boo Applique Shirt and Pants Set</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>3LC26Q34</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Q3 New BtS &amp; Halloween</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="G138" t="n">
+        <v>104</v>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Halloween</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>48922</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Grey Gingham Puppies in Truck Shortalls</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Stage 5</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>4LC26Q22</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Q2 restock</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="G139" t="n">
+        <v>66</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>0.1053</v>
+      </c>
+      <c r="I139" t="n">
+        <v>4</v>
+      </c>
+      <c r="J139" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>47894</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Light Blue Pumpkin Applique Collared Dress</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>4LC26Q32</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>FW26-B&amp;C</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G140" t="n">
+        <v>133</v>
+      </c>
+      <c r="H140" s="3" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" s="3" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>47901</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Red Christmas Plaid Colllared Ruffle Dress</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>4LC26Q32</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>FW26-B&amp;C</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G141" t="n">
+        <v>188</v>
+      </c>
+      <c r="H141" s="3" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>48936</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Light Blue Pumpkin Applique Overalls</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>4LC26Q32</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>FW26-B&amp;C</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G142" t="n">
+        <v>116</v>
+      </c>
+      <c r="H142" s="3" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" s="3" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Thanksgiving</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>38516</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Sage Green Apple Polo Golf Shirt</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>3LC26Q31</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>FW26A BtS &amp; Halloween ReOrder</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="G143" t="n">
+        <v>64</v>
+      </c>
+      <c r="H143" s="3" t="n">
+        <v>0.1533</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Fall/Winter</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>In season</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>31893</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Red Gingham Barn Animals Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>3LC26Q21</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Q2 Reorder</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G144" t="n">
+        <v>111</v>
+      </c>
+      <c r="H144" s="3" t="n">
+        <v>0.4895</v>
+      </c>
+      <c r="I144" t="n">
+        <v>39</v>
+      </c>
+      <c r="J144" s="3" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>32089</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Pink Gingham Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3LC26Q21</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Q2 Reorder</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G145" t="n">
+        <v>146</v>
+      </c>
+      <c r="H145" s="3" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="I145" t="n">
+        <v>53</v>
+      </c>
+      <c r="J145" s="3" t="n">
+        <v>0.5354</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>32553</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>White and Pink Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>3LC26Q21</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Q2 Reorder</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G146" t="n">
+        <v>152</v>
+      </c>
+      <c r="H146" s="3" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="I146" t="n">
+        <v>11</v>
+      </c>
+      <c r="J146" s="3" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>32556</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Pink and White Smocked Bishop Dress</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3LC26Q21</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Q2 Reorder</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G147" t="n">
+        <v>151</v>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="I147" t="n">
+        <v>16</v>
+      </c>
+      <c r="J147" s="3" t="n">
+        <v>0.1391</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>32570</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pink and White Smocked Bubble Romper</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Stage 0</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>3LC26Q21</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Q2 Reorder</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G148" t="n">
+        <v>71</v>
+      </c>
+      <c r="H148" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I148" t="n">
+        <v>9</v>
+      </c>
+      <c r="J148" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>32572</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Pink and White bows Smocked Ruffle Romper</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>3LC26Q21</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Q2 Reorder</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G149" t="n">
+        <v>104</v>
+      </c>
+      <c r="H149" s="3" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="I149" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="3" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>36366</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Light Blue Crosses Smocked Overalls</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3LC26Q21</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Q2 Reorder</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G150" t="n">
+        <v>264</v>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>0.2722</v>
+      </c>
+      <c r="I150" t="n">
+        <v>8</v>
+      </c>
+      <c r="J150" s="3" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>38504</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Light Blue Golf Hole Shirt</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>3LC26Q21</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Q2 Reorder</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G151" t="n">
+        <v>96</v>
+      </c>
+      <c r="H151" s="3" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="I151" t="n">
+        <v>2</v>
+      </c>
+      <c r="J151" s="3" t="n">
+        <v>0.0408</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Year-round</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
           <t>70211</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>White Organic Cotton Short Sleeve Bodysuit</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>Stage 2</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>3LC26Q21</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>Q2 Reorder</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F152" s="2" t="n">
         <v>46168</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G152" t="n">
         <v>147</v>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="H152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t>Year-round</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t>Year-round</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M23"/>
+  <autoFilter ref="A1:M152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/needs-a-push-2026-09-27.xlsx
+++ b/needs-a-push-2026-09-27.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs a Push" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Needs a Push'!$A$1:$M$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Needs a Push'!$A$1:$M$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -518,12 +518,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>47934</t>
+          <t>31807</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sage Green Puppy Dog Petal Smocked Dress</t>
+          <t>Red Christmas Plaid Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -533,54 +533,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4LC26Q33</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FW26 New Fall</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46276</v>
+        <v>46266</v>
       </c>
       <c r="G2" t="n">
-        <v>247</v>
+        <v>312</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.0039</v>
+        <v>0.0427</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0</v>
+        <v>0.2812</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>47935</t>
+          <t>31848</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sage Green Puppy Dog Petal Smocked Romper</t>
+          <t>Navy Blue Nativity Long Sleeve Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -590,54 +590,54 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4LC26Q33</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FW26 New Fall</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46276</v>
+        <v>46266</v>
       </c>
       <c r="G3" t="n">
-        <v>146</v>
+        <v>304</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.013</v>
+        <v>0.0152</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>47936</t>
+          <t>31851</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Golden Wheat Pumpkin Collared Dress</t>
+          <t>Navy Blue Velvet Gold Nativity Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -647,37 +647,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4LC26Q33</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FW26 New Fall</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46276</v>
+        <v>46266</v>
       </c>
       <c r="G4" t="n">
-        <v>244</v>
+        <v>167</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.0156</v>
+        <v>0.0381</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -689,12 +689,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>31852</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Golden Wheat Pumpkin Smocked Petal Collar Dress</t>
+          <t>Green Christmas Mistletoe Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -704,37 +704,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4LC26Q33</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FW26 New Fall</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46276</v>
+        <v>46266</v>
       </c>
       <c r="G5" t="n">
-        <v>250</v>
+        <v>688</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.0078</v>
+        <v>0.0337</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -746,12 +746,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>47938</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Golden Wheat Pumpkin Smocked Petal Collar Romper</t>
+          <t>Red Velvet Christmas Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,37 +761,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4LC26Q33</t>
+          <t>3LC26Q33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FW26 New Fall</t>
+          <t>FW26 Ship C</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46276</v>
+        <v>46266</v>
       </c>
       <c r="G6" t="n">
-        <v>147</v>
+        <v>723</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -803,12 +803,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>31807</t>
+          <t>31903</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Red Christmas Plaid Smocked Bishop Dress</t>
+          <t>Navy Blue Santa Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -830,16 +830,16 @@
         <v>46266</v>
       </c>
       <c r="G7" t="n">
-        <v>312</v>
+        <v>370</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.0427</v>
+        <v>0.0123</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.2812</v>
+        <v>0.8571</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -860,12 +860,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>31848</t>
+          <t>32059</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Navy Blue Nativity Long Sleeve Smocked Bishop Dress</t>
+          <t>Red Poplin Santa Long Sleeve Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,20 +887,20 @@
         <v>46266</v>
       </c>
       <c r="G8" t="n">
-        <v>304</v>
+        <v>471</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.0152</v>
+        <v>0.0057</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>31851</t>
+          <t>32126</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Navy Blue Velvet Gold Nativity Smocked Bishop Dress</t>
+          <t>Red &amp; White Santa Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -944,20 +944,20 @@
         <v>46266</v>
       </c>
       <c r="G9" t="n">
-        <v>167</v>
+        <v>366</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.0381</v>
+        <v>0.0174</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.125</v>
+        <v>0.875</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -974,12 +974,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>31852</t>
+          <t>32223</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Green Christmas Mistletoe Smocked Bishop Dress</t>
+          <t>Pink Christmas Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1001,20 +1001,20 @@
         <v>46266</v>
       </c>
       <c r="G10" t="n">
-        <v>688</v>
+        <v>302</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.0337</v>
+        <v>0.0047</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1031,12 +1031,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>31896</t>
+          <t>32279</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Red Velvet Christmas Smocked Bishop Dress</t>
+          <t>Light Blue Smocked Nativity Collared Dress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,20 +1058,20 @@
         <v>46266</v>
       </c>
       <c r="G11" t="n">
-        <v>723</v>
+        <v>117</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.0063</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1088,12 +1088,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>31903</t>
+          <t>32501</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Navy Blue Santa Smocked Bishop Dress</t>
+          <t>Green Velvet Santa Smocked Dress</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1115,20 +1115,20 @@
         <v>46266</v>
       </c>
       <c r="G12" t="n">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.0123</v>
+        <v>0.0069</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.8571</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1145,12 +1145,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>32502</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Red Poplin Santa Long Sleeve Smocked Bishop Dress</t>
+          <t>Light Blue Christmas Tree Smocked Knit Dress</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1172,10 +1172,10 @@
         <v>46266</v>
       </c>
       <c r="G13" t="n">
-        <v>471</v>
+        <v>126</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.0057</v>
+        <v>0.0048</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1202,12 +1202,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>32126</t>
+          <t>32504</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Red &amp; White Santa Smocked Bishop Dress</t>
+          <t>Green Velvet Santa Smocked Dress and Bloomers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1229,20 +1229,20 @@
         <v>46266</v>
       </c>
       <c r="G14" t="n">
-        <v>366</v>
+        <v>258</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.0174</v>
+        <v>0.0074</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1259,12 +1259,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>32223</t>
+          <t>32507</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pink Christmas Smocked Bishop Dress</t>
+          <t>Light Blue Christmas Tree Smocked Knit Ruffle Romper</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1286,10 +1286,10 @@
         <v>46266</v>
       </c>
       <c r="G15" t="n">
-        <v>302</v>
+        <v>109</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.0047</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1316,12 +1316,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>32279</t>
+          <t>32508</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Light Blue Smocked Nativity Collared Dress</t>
+          <t>Dark Blue Nativity Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1343,20 +1343,20 @@
         <v>46266</v>
       </c>
       <c r="G16" t="n">
-        <v>117</v>
+        <v>285</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0</v>
+        <v>0.0054</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1373,12 +1373,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>32501</t>
+          <t>32509</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Green Velvet Santa Smocked Dress</t>
+          <t>Red Velvet Gold Nativity Smocked Dress</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1400,20 +1400,20 @@
         <v>46266</v>
       </c>
       <c r="G17" t="n">
-        <v>353</v>
+        <v>264</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.0069</v>
+        <v>0.0167</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1430,12 +1430,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>32502</t>
+          <t>32520</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Light Blue Christmas Tree Smocked Knit Dress</t>
+          <t>Green Christmas Tree Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1457,10 +1457,10 @@
         <v>46266</v>
       </c>
       <c r="G18" t="n">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.0048</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1487,12 +1487,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>32504</t>
+          <t>32521</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Green Velvet Santa Smocked Dress and Bloomers</t>
+          <t>Red Santa Sleigh Bishop Dress</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1514,20 +1514,20 @@
         <v>46266</v>
       </c>
       <c r="G19" t="n">
-        <v>258</v>
+        <v>143</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.0074</v>
+        <v>0.0111</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1544,12 +1544,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>32507</t>
+          <t>32524</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Light Blue Christmas Tree Smocked Knit Ruffle Romper</t>
+          <t>Red and Green Christmas Plaid Smocked Dress</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1571,7 +1571,7 @@
         <v>46266</v>
       </c>
       <c r="G20" t="n">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0</v>
@@ -1601,12 +1601,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>32508</t>
+          <t>32590</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dark Blue Nativity Smocked Bishop Dress</t>
+          <t>Pink Hearts &amp; Bows Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1631,10 +1631,10 @@
         <v>285</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.0054</v>
+        <v>0.0034</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>1</v>
@@ -1646,24 +1646,24 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Christmas</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>32509</t>
+          <t>33226</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Red Velvet Gold Nativity Smocked Dress</t>
+          <t>Red Santa Smocked Ruffle Bishop Dress</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1685,20 +1685,20 @@
         <v>46266</v>
       </c>
       <c r="G22" t="n">
-        <v>264</v>
+        <v>219</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.0167</v>
+        <v>0.0031</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1715,12 +1715,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>32520</t>
+          <t>33227</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Green Christmas Tree Smocked Bishop Dress</t>
+          <t>Red Santa Smocked Ruffle Romper</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1742,10 +1742,10 @@
         <v>46266</v>
       </c>
       <c r="G23" t="n">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1772,12 +1772,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>32521</t>
+          <t>33228</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Red Santa Sleigh Bishop Dress</t>
+          <t>Blue Nativity Smocked Ruffle Bishop Dress</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1799,16 +1799,16 @@
         <v>46266</v>
       </c>
       <c r="G24" t="n">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.0111</v>
+        <v>0.0333</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.5</v>
+        <v>0.2143</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1829,12 +1829,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>32524</t>
+          <t>33229</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Red and Green Christmas Plaid Smocked Dress</t>
+          <t>Red Corduroy Mistletoe Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1856,20 +1856,20 @@
         <v>46266</v>
       </c>
       <c r="G25" t="n">
-        <v>170</v>
+        <v>385</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0</v>
+        <v>0.0378</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0</v>
+        <v>0.8235</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1886,12 +1886,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>32590</t>
+          <t>33230</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pink Hearts &amp; Bows Smocked Bishop Dress</t>
+          <t>Green Corduroy Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1913,13 +1913,13 @@
         <v>46266</v>
       </c>
       <c r="G26" t="n">
-        <v>285</v>
+        <v>420</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.0034</v>
+        <v>0.0111</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>1</v>
@@ -1931,24 +1931,24 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>33231</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Red Santa Smocked Ruffle Bishop Dress</t>
+          <t>Blue Velvet Silver Bows Smocked Ruffle Bishop Dress</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1970,20 +1970,20 @@
         <v>46266</v>
       </c>
       <c r="G27" t="n">
-        <v>219</v>
+        <v>319</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.0031</v>
+        <v>0.0286</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2000,12 +2000,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>33227</t>
+          <t>33232</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Red Santa Smocked Ruffle Romper</t>
+          <t>Green Velvet Christmas Tree Ruffle Dress</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2027,10 +2027,10 @@
         <v>46266</v>
       </c>
       <c r="G28" t="n">
-        <v>95</v>
+        <v>309</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.0067</v>
+        <v>0.0045</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2057,12 +2057,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>33228</t>
+          <t>33233</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Blue Nativity Smocked Ruffle Bishop Dress</t>
+          <t>Blue Nativity Smocked Ruffle Romper</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2084,16 +2084,16 @@
         <v>46266</v>
       </c>
       <c r="G29" t="n">
-        <v>201</v>
+        <v>103</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.0333</v>
+        <v>0.0077</v>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.2143</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2114,12 +2114,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>33229</t>
+          <t>33234</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Red Corduroy Mistletoe Smocked Bishop Dress</t>
+          <t>Red Bishop Dress Christmas Bows Smocked Ruffle Bishop Dress</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2141,20 +2141,20 @@
         <v>46266</v>
       </c>
       <c r="G30" t="n">
-        <v>385</v>
+        <v>310</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.0378</v>
+        <v>0.0194</v>
       </c>
       <c r="I30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.8235</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2171,12 +2171,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>33230</t>
+          <t>33762</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Green Corduroy Smocked Bishop Dress</t>
+          <t>Light Blue Nativity Smocked Overalls</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2198,20 +2198,20 @@
         <v>46266</v>
       </c>
       <c r="G31" t="n">
-        <v>420</v>
+        <v>143</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.0111</v>
+        <v>0.028</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1</v>
+        <v>0.1429</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2228,12 +2228,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>33231</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Blue Velvet Silver Bows Smocked Ruffle Bishop Dress</t>
+          <t>Red Velvet Christmas Smocked Overalls</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2255,16 +2255,16 @@
         <v>46266</v>
       </c>
       <c r="G32" t="n">
-        <v>319</v>
+        <v>271</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.0286</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2285,12 +2285,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>33232</t>
+          <t>33913</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Green Velvet Christmas Tree Ruffle Dress</t>
+          <t>Red and White Santa Smocked Overalls</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2312,10 +2312,10 @@
         <v>46266</v>
       </c>
       <c r="G33" t="n">
-        <v>309</v>
+        <v>115</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.0045</v>
+        <v>0.02</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -2342,12 +2342,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33233</t>
+          <t>35316</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Blue Nativity Smocked Ruffle Romper</t>
+          <t>Dark Blue Nativity Smocked Overalls</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2369,16 +2369,16 @@
         <v>46266</v>
       </c>
       <c r="G34" t="n">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.0077</v>
+        <v>0.0556</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2399,12 +2399,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>35356</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Red Bishop Dress Christmas Bows Smocked Ruffle Bishop Dress</t>
+          <t>Green Christmas Smocked Overalls</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2426,20 +2426,20 @@
         <v>46266</v>
       </c>
       <c r="G35" t="n">
-        <v>310</v>
+        <v>262</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.0194</v>
+        <v>0.0262</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2456,12 +2456,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>33762</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Light Blue Nativity Smocked Overalls</t>
+          <t>Red Plaid Truck &amp; Tree Smocked Overalls</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2483,20 +2483,20 @@
         <v>46266</v>
       </c>
       <c r="G36" t="n">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>33770</t>
+          <t>36340</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Red Velvet Christmas Smocked Overalls</t>
+          <t>Navy Blue Santa Smocked Overalls</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2540,16 +2540,16 @@
         <v>46266</v>
       </c>
       <c r="G37" t="n">
-        <v>271</v>
+        <v>194</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0161</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.8</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2570,12 +2570,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>33913</t>
+          <t>36378</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Red and White Santa Smocked Overalls</t>
+          <t>Red and Green Christmas Plaid Smocked Overalls</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2597,10 +2597,10 @@
         <v>46266</v>
       </c>
       <c r="G38" t="n">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2627,12 +2627,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>35316</t>
+          <t>36379</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dark Blue Nativity Smocked Overalls</t>
+          <t>Green Corduroy Santa Smocked Overalls</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2654,16 +2654,16 @@
         <v>46266</v>
       </c>
       <c r="G39" t="n">
-        <v>133</v>
+        <v>349</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.0556</v>
+        <v>0.0407</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.5</v>
+        <v>0.2727</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2684,12 +2684,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>35356</t>
+          <t>36381</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Green Christmas Smocked Overalls</t>
+          <t>Light Blue Nativity Overalls</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2711,20 +2711,20 @@
         <v>46266</v>
       </c>
       <c r="G40" t="n">
-        <v>262</v>
+        <v>113</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.0262</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2741,12 +2741,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>35456</t>
+          <t>36383</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Red Plaid Truck &amp; Tree Smocked Overalls</t>
+          <t>Red Santa Sleigh Overalls</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2768,7 +2768,7 @@
         <v>46266</v>
       </c>
       <c r="G41" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0</v>
@@ -2798,12 +2798,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>36340</t>
+          <t>36507</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Navy Blue Santa Smocked Overalls</t>
+          <t>Red Santa Smocked Overalls</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2825,16 +2825,16 @@
         <v>46266</v>
       </c>
       <c r="G42" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.0161</v>
+        <v>0.0069</v>
       </c>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2855,12 +2855,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>36378</t>
+          <t>36508</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Red and Green Christmas Plaid Smocked Overalls</t>
+          <t>Blue Nativity Smocked Overalls</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2882,20 +2882,20 @@
         <v>46266</v>
       </c>
       <c r="G43" t="n">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0</v>
+        <v>0.0241</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2912,12 +2912,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>36379</t>
+          <t>36509</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Green Corduroy Santa Smocked Overalls</t>
+          <t>Red Corduroy Mistletoe Smocked Overalls</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2939,20 +2939,20 @@
         <v>46266</v>
       </c>
       <c r="G44" t="n">
-        <v>349</v>
+        <v>142</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.0407</v>
+        <v>0.0067</v>
       </c>
       <c r="I44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.2727</v>
+        <v>0</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2969,12 +2969,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>36381</t>
+          <t>36520</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Light Blue Nativity Overalls</t>
+          <t>Green Corduroy Santa Dress Shirt</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2996,10 +2996,10 @@
         <v>46266</v>
       </c>
       <c r="G45" t="n">
-        <v>113</v>
+        <v>349</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0</v>
+        <v>0.0404</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -3026,12 +3026,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>36383</t>
+          <t>36522</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Red Santa Sleigh Overalls</t>
+          <t>Sand Beige Reindeer Dress Shirt</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3053,7 +3053,7 @@
         <v>46266</v>
       </c>
       <c r="G46" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0</v>
@@ -3083,12 +3083,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>36507</t>
+          <t>38075</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Red Santa Smocked Overalls</t>
+          <t>Beige Nativity Smocked Shirt and Blue Pants</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3110,20 +3110,20 @@
         <v>46266</v>
       </c>
       <c r="G47" t="n">
-        <v>210</v>
+        <v>114</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.0069</v>
+        <v>0.0143</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3140,12 +3140,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>36508</t>
+          <t>38081</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Blue Nativity Smocked Overalls</t>
+          <t>Red Santa Smocked Shirt and Navy Pants Set</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3167,20 +3167,20 @@
         <v>46266</v>
       </c>
       <c r="G48" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.0241</v>
+        <v>0.008</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3197,12 +3197,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>36509</t>
+          <t>38111</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Red Corduroy Mistletoe Smocked Overalls</t>
+          <t xml:space="preserve"> Sand Beige Reindeer Shirt and Brown Pants Set</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3224,10 +3224,10 @@
         <v>46266</v>
       </c>
       <c r="G49" t="n">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.0067</v>
+        <v>0.0526</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -3254,12 +3254,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>36520</t>
+          <t>75720</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Green Corduroy Santa Dress Shirt</t>
+          <t>Red Christmas Tree Knit Cardigan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3281,10 +3281,10 @@
         <v>46266</v>
       </c>
       <c r="G50" t="n">
-        <v>349</v>
+        <v>128</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.0404</v>
+        <v>0.0111</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -3311,12 +3311,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>36522</t>
+          <t>75721</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sand Beige Reindeer Dress Shirt</t>
+          <t>Navy Blue Christmas Santa Knit Cardigan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3338,20 +3338,20 @@
         <v>46266</v>
       </c>
       <c r="G51" t="n">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3368,12 +3368,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>38075</t>
+          <t>61010</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Beige Nativity Smocked Shirt and Blue Pants</t>
+          <t>Pink Sparkly Bow Sweater</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3383,22 +3383,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3LC26Q33</t>
+          <t>6LC26Q32</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FW26 Ship C</t>
+          <t>FW26 Christmas</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>46266</v>
       </c>
       <c r="G52" t="n">
-        <v>114</v>
+        <v>238</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.0143</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -3413,24 +3413,24 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Christmas</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>38081</t>
+          <t>61013</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Red Santa Smocked Shirt and Navy Pants Set</t>
+          <t>Red Sweater with Glitter Bow</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3440,22 +3440,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3LC26Q33</t>
+          <t>6LC26Q32</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FW26 Ship C</t>
+          <t>FW26 Christmas</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>46266</v>
       </c>
       <c r="G53" t="n">
-        <v>143</v>
+        <v>297</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.008</v>
+        <v>0.0362</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -3482,12 +3482,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>61014</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sand Beige Reindeer Shirt and Brown Pants Set</t>
+          <t>Red Santa Sweater</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3497,22 +3497,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3LC26Q33</t>
+          <t>6LC26Q32</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FW26 Ship C</t>
+          <t>FW26 Christmas</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>46266</v>
       </c>
       <c r="G54" t="n">
-        <v>96</v>
+        <v>242</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.0526</v>
+        <v>0.0267</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -3539,12 +3539,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>75720</t>
+          <t>61016</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Red Christmas Tree Knit Cardigan</t>
+          <t>Pink Reindeer Sweater</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3554,32 +3554,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3LC26Q33</t>
+          <t>6LC26Q32</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FW26 Ship C</t>
+          <t>FW26 Christmas</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
         <v>46266</v>
       </c>
       <c r="G55" t="n">
-        <v>128</v>
+        <v>203</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.0111</v>
+        <v>0.0667</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0</v>
+        <v>0.0556</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3596,12 +3596,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>75721</t>
+          <t>61017</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Navy Blue Christmas Santa Knit Cardigan</t>
+          <t>Green Santa Christmas Sweater</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3LC26Q33</t>
+          <t>6LC26Q32</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FW26 Ship C</t>
+          <t>FW26 Christmas</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
         <v>46266</v>
       </c>
       <c r="G56" t="n">
-        <v>144</v>
+        <v>229</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.008</v>
+        <v>0.0895</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3653,12 +3653,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>61010</t>
+          <t>61018</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pink Sparkly Bow Sweater</t>
+          <t>Blue Reindeer Christmas Sweater</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3680,10 +3680,10 @@
         <v>46266</v>
       </c>
       <c r="G57" t="n">
-        <v>238</v>
+        <v>167</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0278</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -3698,24 +3698,24 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>61013</t>
+          <t>61023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Red Sweater with Glitter Bow</t>
+          <t>Blue Sparkly Bow Sweater</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3737,10 +3737,10 @@
         <v>46266</v>
       </c>
       <c r="G58" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.0362</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -3755,24 +3755,24 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Christmas</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>61014</t>
+          <t>61024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Red Santa Sweater</t>
+          <t>Cream Sparkly Bow Sweater</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3794,10 +3794,10 @@
         <v>46266</v>
       </c>
       <c r="G59" t="n">
-        <v>242</v>
+        <v>300</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.0267</v>
+        <v>0.0067</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -3812,24 +3812,24 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Christmas</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>61016</t>
+          <t>33296</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pink Reindeer Sweater</t>
+          <t>Heritage Rose Ruffle Smocked Dress</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3839,54 +3839,54 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>6LC26Q32</t>
+          <t>3LC26Q35</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FW26 Christmas</t>
+          <t>FW26- New Thankgiving</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="G60" t="n">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.0667</v>
+        <v>0.0456</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.0556</v>
+        <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Christmas</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>61017</t>
+          <t>33297</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Green Santa Christmas Sweater</t>
+          <t>Heritage Rose Ruffle Smocked Romper</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3896,22 +3896,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>6LC26Q32</t>
+          <t>3LC26Q35</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FW26 Christmas</t>
+          <t>FW26- New Thankgiving</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="G61" t="n">
-        <v>229</v>
+        <v>130</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.0895</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -3926,24 +3926,24 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Christmas</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>61018</t>
+          <t>33298</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Blue Reindeer Christmas Sweater</t>
+          <t>Heritage Rose Ruffle Smocked Playsuit</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3953,22 +3953,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>6LC26Q32</t>
+          <t>3LC26Q35</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FW26 Christmas</t>
+          <t>FW26- New Thankgiving</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="G62" t="n">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.0278</v>
+        <v>0.0604</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -3983,24 +3983,24 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Christmas</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>61023</t>
+          <t>36546</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blue Sparkly Bow Sweater</t>
+          <t>Heritage Blue Puppy Dog Overalls</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4010,22 +4010,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6LC26Q32</t>
+          <t>3LC26Q35</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FW26 Christmas</t>
+          <t>FW26- New Thankgiving</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="G63" t="n">
-        <v>301</v>
+        <v>141</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -4052,12 +4052,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>61024</t>
+          <t>38131</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cream Sparkly Bow Sweater</t>
+          <t>Pistachio Green Mallard Duck Smocked Shirt and Shorts Set</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4067,22 +4067,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>6LC26Q32</t>
+          <t>3LC26Q35</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FW26 Christmas</t>
+          <t>FW26- New Thankgiving</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="G64" t="n">
-        <v>300</v>
+        <v>124</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.0067</v>
+        <v>0.0533</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -4097,24 +4097,24 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Fall/Winter</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>33287</t>
+          <t>75731</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sage Green Pumpkin Smocked Ruffle Dress</t>
+          <t>Heirloom Pink Roses Collared Sweater</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4136,25 +4136,25 @@
         <v>46259</v>
       </c>
       <c r="G65" t="n">
-        <v>101</v>
+        <v>252</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.332</v>
+        <v>0.09</v>
       </c>
       <c r="I65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.0482</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Fall/Winter</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4166,12 +4166,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>33288</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sage Green Pumpkin Smocked Ruffle Romper</t>
+          <t>Sage Green Turkey Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4181,32 +4181,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G66" t="n">
-        <v>71</v>
+        <v>352</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.2467</v>
+        <v>0.1414</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0</v>
+        <v>0.2174</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4223,12 +4223,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>33292</t>
+          <t>31898</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Heritage Custom Rose Smocked Bishop Dress</t>
+          <t>Blue Pumpkin Gingham Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4238,28 +4238,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G67" t="n">
-        <v>153</v>
+        <v>254</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1325</v>
+        <v>0.2163</v>
       </c>
       <c r="I67" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.2121</v>
+        <v>0.3366</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -4268,24 +4268,24 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>33293</t>
+          <t>31899</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Heritage Custom Rose Layered Ruffle Dress</t>
+          <t>Sage Green Pumpkin Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4295,54 +4295,54 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G68" t="n">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1004</v>
+        <v>0.3655</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>0.4494</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>33296</t>
+          <t>31900</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Heritage Rose Ruffle Smocked Dress</t>
+          <t>Cobalt Blue Turkey Bishop Dress</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4352,54 +4352,54 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G69" t="n">
-        <v>230</v>
+        <v>263</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.0456</v>
+        <v>0.0605</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>33297</t>
+          <t>31906</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Heritage Rose Ruffle Smocked Romper</t>
+          <t>Light Blue Puppy Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4409,32 +4409,32 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G70" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.1656</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4451,12 +4451,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>33298</t>
+          <t>31907</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Heritage Rose Ruffle Smocked Playsuit</t>
+          <t>Sage Green Mallard Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4466,54 +4466,54 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G71" t="n">
-        <v>131</v>
+        <v>317</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.0604</v>
+        <v>0.1795</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.2674</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Fall/Winter</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>33309</t>
+          <t>31987</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Red and Cream Gingham Farm Smocked Dress</t>
+          <t>Light Brown Smocked Ruffle Dress</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4523,32 +4523,32 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G72" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.14</v>
+        <v>0.1589</v>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.0857</v>
+        <v>0.2195</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4565,52 +4565,52 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>33310</t>
+          <t>31988</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pistachio Green Mallard Duck Smocked Bishop Dress</t>
+          <t>Light Brown Pinstripe Pumpkin Smocked Dress and Bloomer Set</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G73" t="n">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.324</v>
+        <v>0.2548</v>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.0617</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Fall/Winter</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -4622,47 +4622,47 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>36524</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cream Pumpkin Dress Shirt</t>
+          <t>Light Blue Pumpkin Vine Smocked Dress and Bloomers</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G74" t="n">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1313</v>
+        <v>0.3202</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0</v>
+        <v>0.0351</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4679,12 +4679,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>36546</t>
+          <t>31994</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Heritage Blue Puppy Dog Overalls</t>
+          <t>Blue and Pink Bow Smocked Romper</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4694,32 +4694,32 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G75" t="n">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.0068</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4736,12 +4736,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>36548</t>
+          <t>32277</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sage Green Puppy Dog Overalls</t>
+          <t>Light Brown Gingham Pumpkin Vine Ruffle Dress</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4751,28 +4751,28 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G76" t="n">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1333</v>
+        <v>0.1272</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1724</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -4781,24 +4781,24 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>36549</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sage Green Pumpkin Smocked Jon-Jons</t>
+          <t>Light Blue Pumpkin Vine Smocked Dress</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4808,28 +4808,28 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G77" t="n">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.3467</v>
+        <v>0.1591</v>
       </c>
       <c r="I77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.1346</v>
+        <v>0.1224</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -4850,12 +4850,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>32597</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Red and Cream Gingham Farm Overalls</t>
+          <t>Brown Floral Tunic and Leggings Set</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4865,22 +4865,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G78" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.2867</v>
+        <v>0.1149</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -4907,12 +4907,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>36554</t>
+          <t>32598</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pistachio Green Mallard Duck Smocked Overalls</t>
+          <t>Brown Floral Smocked. Bishop Dress</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4922,32 +4922,32 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G79" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.2933</v>
+        <v>0.3649</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0.0227</v>
+        <v>0.2222</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4964,12 +4964,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>38131</t>
+          <t>33053</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pistachio Green Mallard Duck Smocked Shirt and Shorts Set</t>
+          <t>White Cotton Heirloom Bloomers</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4979,22 +4979,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G80" t="n">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.0533</v>
+        <v>0.0342</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
@@ -5009,24 +5009,24 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Fall/Winter</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>75731</t>
+          <t>33224</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Heirloom Pink Roses Collared Sweater</t>
+          <t>Light Blue Gingham Smocked Dress</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5036,22 +5036,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>3LC26Q35</t>
+          <t>3LC26Q32</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>FW26- New Thankgiving</t>
+          <t>FW26-B (Fall)</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="G81" t="n">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1046</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
@@ -5066,24 +5066,24 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Fall/Winter</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>33225</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sage Green Turkey Smocked Bishop Dress</t>
+          <t>Light Brown Pumpkin Smocked Collared Dress</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5105,16 +5105,16 @@
         <v>46230</v>
       </c>
       <c r="G82" t="n">
-        <v>352</v>
+        <v>226</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.1414</v>
+        <v>0.2332</v>
       </c>
       <c r="I82" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>0.2174</v>
+        <v>0.5778</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -5135,12 +5135,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>31898</t>
+          <t>33761</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Blue Pumpkin Gingham Smocked Bishop Dress</t>
+          <t>Sage Green Turkey Smocked Overalls</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5162,16 +5162,16 @@
         <v>46230</v>
       </c>
       <c r="G83" t="n">
-        <v>254</v>
+        <v>194</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.2163</v>
+        <v>0.0968</v>
       </c>
       <c r="I83" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.3366</v>
+        <v>0.2083</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -5192,12 +5192,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>31899</t>
+          <t>34726</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sage Green Pumpkin Smocked Bishop Dress</t>
+          <t>Blue Pinstripe Smocked Ruffle Collar Dress</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5219,25 +5219,25 @@
         <v>46230</v>
       </c>
       <c r="G84" t="n">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.3655</v>
+        <v>0.3156</v>
       </c>
       <c r="I84" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.4494</v>
+        <v>0.1345</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Fall/Winter</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5249,12 +5249,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>31900</t>
+          <t>36337</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cobalt Blue Turkey Bishop Dress</t>
+          <t>Blue Pumpkin Overalls</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5276,20 +5276,20 @@
         <v>46230</v>
       </c>
       <c r="G85" t="n">
-        <v>263</v>
+        <v>86</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.0605</v>
+        <v>0.1645</v>
       </c>
       <c r="I85" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.625</v>
+        <v>0.0789</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5306,12 +5306,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>31906</t>
+          <t>36338</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Light Blue Puppy Smocked Bishop Dress</t>
+          <t>Cobalt Blue Turkey Smocked Overalls</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5333,42 +5333,42 @@
         <v>46230</v>
       </c>
       <c r="G86" t="n">
-        <v>200</v>
+        <v>122</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.1656</v>
+        <v>0.1709</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1765</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>31907</t>
+          <t>36348</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sage Green Mallard Smocked Bishop Dress</t>
+          <t>Sage Green Mallard Smocked Overalls</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5390,20 +5390,20 @@
         <v>46230</v>
       </c>
       <c r="G87" t="n">
-        <v>317</v>
+        <v>104</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.1795</v>
+        <v>0.2149</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.2674</v>
+        <v>0.0408</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5420,12 +5420,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>31987</t>
+          <t>36360</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Light Brown Smocked Ruffle Dress</t>
+          <t>Light Brown Mallard Smocked Overalls</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5447,47 +5447,47 @@
         <v>46230</v>
       </c>
       <c r="G88" t="n">
-        <v>159</v>
+        <v>111</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.1589</v>
+        <v>0.1066</v>
       </c>
       <c r="I88" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.2195</v>
+        <v>0.1429</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Fall/Winter</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>31988</t>
+          <t>36364</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Light Brown Pinstripe Pumpkin Smocked Dress and Bloomer Set</t>
+          <t>Light Gray Mallard Smocked Overalls</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5504,25 +5504,25 @@
         <v>46230</v>
       </c>
       <c r="G89" t="n">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>0.2548</v>
+        <v>0.0946</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Fall/Winter</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -5534,17 +5534,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>31990</t>
+          <t>36365</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Light Blue Pumpkin Vine Smocked Dress and Bloomers</t>
+          <t>Light Green Alligator Smocked Overalls</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5561,16 +5561,16 @@
         <v>46230</v>
       </c>
       <c r="G90" t="n">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.3202</v>
+        <v>0.2</v>
       </c>
       <c r="I90" t="n">
         <v>2</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.0351</v>
+        <v>0.0833</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -5579,29 +5579,29 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Blue and Pink Bow Smocked Romper</t>
+          <t>Light Blue Crosses Smocked Overalls</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5618,20 +5618,20 @@
         <v>46230</v>
       </c>
       <c r="G91" t="n">
-        <v>123</v>
+        <v>264</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -5648,17 +5648,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>32277</t>
+          <t>36368</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Light Brown Gingham Pumpkin Vine Ruffle Dress</t>
+          <t>Sage Green Construction Smocked Overalls</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5675,16 +5675,16 @@
         <v>46230</v>
       </c>
       <c r="G92" t="n">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.1272</v>
+        <v>0.2162</v>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.1724</v>
+        <v>0.1875</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -5693,24 +5693,24 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>32278</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Light Blue Pumpkin Vine Smocked Dress</t>
+          <t>Light Brown Pinstripe Pumpkin Smocked Overalls</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5732,20 +5732,20 @@
         <v>46230</v>
       </c>
       <c r="G93" t="n">
-        <v>212</v>
+        <v>90</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.1591</v>
+        <v>0.2548</v>
       </c>
       <c r="I93" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>0.1224</v>
+        <v>0.2075</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5762,12 +5762,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>32597</t>
+          <t>36395</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Brown Floral Tunic and Leggings Set</t>
+          <t>Light Blue Pinstripe Turkey Smocked Overalls</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5789,25 +5789,25 @@
         <v>46230</v>
       </c>
       <c r="G94" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.1149</v>
+        <v>0.1164</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>0</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Fall/Winter</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -5819,12 +5819,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>32598</t>
+          <t>36501</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Brown Floral Smocked. Bishop Dress</t>
+          <t>Blue Pinstripe Mallard Duck Smocked Overalls</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5846,20 +5846,20 @@
         <v>46230</v>
       </c>
       <c r="G95" t="n">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.3649</v>
+        <v>0.2586</v>
       </c>
       <c r="I95" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.2222</v>
+        <v>0.1939</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5876,12 +5876,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>33053</t>
+          <t>36502</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>White Cotton Heirloom Bloomers</t>
+          <t>Blue Gingham Train Smocked Overalls</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5903,20 +5903,20 @@
         <v>46230</v>
       </c>
       <c r="G96" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.0342</v>
+        <v>0.2275</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0</v>
+        <v>0.4737</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5933,12 +5933,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>33224</t>
+          <t>36506</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Light Blue Gingham Smocked Dress</t>
+          <t>Brown Turkey Face Overalls</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5960,42 +5960,42 @@
         <v>46230</v>
       </c>
       <c r="G97" t="n">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0.1046</v>
+        <v>0.0798</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>0</v>
+        <v>0.1333</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>33225</t>
+          <t>38074</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Light Brown Pumpkin Smocked Collared Dress</t>
+          <t>Light Brown Turkey Shirt and Sage Green Pants Set</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6017,20 +6017,20 @@
         <v>46230</v>
       </c>
       <c r="G98" t="n">
-        <v>226</v>
+        <v>140</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>0.2332</v>
+        <v>0.1422</v>
       </c>
       <c r="I98" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>0.5778</v>
+        <v>0.1613</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6047,12 +6047,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>33761</t>
+          <t>38091</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sage Green Turkey Smocked Overalls</t>
+          <t>Light Gray Mallard Smocked Shirt and Pants</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6074,25 +6074,25 @@
         <v>46230</v>
       </c>
       <c r="G99" t="n">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>0.0968</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.2083</v>
+        <v>0</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Fall/Winter</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -6104,12 +6104,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>34726</t>
+          <t>38097</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Blue Pinstripe Smocked Ruffle Collar Dress</t>
+          <t>White Football Truck Shirt and Brown Pants Set</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6131,16 +6131,16 @@
         <v>46230</v>
       </c>
       <c r="G100" t="n">
-        <v>175</v>
+        <v>62</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0.3156</v>
+        <v>0.1034</v>
       </c>
       <c r="I100" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.1345</v>
+        <v>0.0833</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Fall/Winter</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -6161,17 +6161,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>36337</t>
+          <t>38504</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Blue Pumpkin Overalls</t>
+          <t>Light Blue Golf Hole Shirt</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6188,42 +6188,42 @@
         <v>46230</v>
       </c>
       <c r="G101" t="n">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0.1645</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0.0789</v>
+        <v>0</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>36338</t>
+          <t>38505</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cobalt Blue Turkey Smocked Overalls</t>
+          <t>Sage Green Mallard Polo Shirt</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6245,16 +6245,16 @@
         <v>46230</v>
       </c>
       <c r="G102" t="n">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>0.1709</v>
+        <v>0.1429</v>
       </c>
       <c r="I102" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>0.1765</v>
+        <v>0.0833</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -6263,24 +6263,24 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>36348</t>
+          <t>38517</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sage Green Mallard Smocked Overalls</t>
+          <t>Brown Turkey Face T-Shirt</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6302,25 +6302,25 @@
         <v>46230</v>
       </c>
       <c r="G103" t="n">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0.2149</v>
+        <v>0.1271</v>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0.0408</v>
+        <v>0</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Fall/Winter</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -6332,12 +6332,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>36360</t>
+          <t>38518</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Light Brown Mallard Smocked Overalls</t>
+          <t>Sand Beige Pumpkin Tractor Polo Golf Shirt</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6359,42 +6359,42 @@
         <v>46230</v>
       </c>
       <c r="G104" t="n">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>0.1066</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="I104" t="n">
         <v>3</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.1429</v>
+        <v>0.3333</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>36364</t>
+          <t>70214</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Light Gray Mallard Smocked Overalls</t>
+          <t>White Lace Collared Girls Long Sleeve Bodysuit Romper</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6416,16 +6416,16 @@
         <v>46230</v>
       </c>
       <c r="G105" t="n">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>0.0946</v>
+        <v>0.0743</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -6434,24 +6434,24 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Fall/Winter</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>36365</t>
+          <t>70226</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Light Green Alligator Smocked Overalls</t>
+          <t>White Pointed Collar Button Romper</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6473,16 +6473,16 @@
         <v>46230</v>
       </c>
       <c r="G106" t="n">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.2</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.0833</v>
+        <v>0.1111</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -6503,47 +6503,47 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>36366</t>
+          <t>33890</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Light Blue Crosses Smocked Overalls</t>
+          <t>Light Blue Gingham Basic Baby Jon Jon</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Stage 2</t>
+          <t>Stage 5</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q23</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q2 ReOrder</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>46230</v>
+        <v>46221</v>
       </c>
       <c r="G107" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>0.7531</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6560,12 +6560,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>36368</t>
+          <t>34343</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sage Green Construction Smocked Overalls</t>
+          <t>Green Gingham Alligator Bubble Romper</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6575,28 +6575,28 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q23</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q2 ReOrder</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>46230</v>
+        <v>46221</v>
       </c>
       <c r="G108" t="n">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>0.2162</v>
+        <v>0.35</v>
       </c>
       <c r="I108" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>0.1875</v>
+        <v>0.1948</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -6617,214 +6617,214 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>36374</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Light Brown Pinstripe Pumpkin Smocked Overalls</t>
+          <t>Light Blue Seersucker Ruffle Dress</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 2</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q23</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q2 ReOrder</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>46230</v>
+        <v>46221</v>
       </c>
       <c r="G109" t="n">
-        <v>90</v>
+        <v>166</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>0.2548</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>0.2075</v>
+        <v>0</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>36395</t>
+          <t>36386</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Light Blue Pinstripe Turkey Smocked Overalls</t>
+          <t>White and Blue Holy Smocked Overalls</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q23</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q2 ReOrder</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>46230</v>
+        <v>46221</v>
       </c>
       <c r="G110" t="n">
-        <v>87</v>
+        <v>196</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0.1164</v>
+        <v>0.1708</v>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>36501</t>
+          <t>36532</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Blue Pinstripe Mallard Duck Smocked Overalls</t>
+          <t>Blue Crosses Smocked JonJon</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 5</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q23</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q2 ReOrder</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>46230</v>
+        <v>46221</v>
       </c>
       <c r="G111" t="n">
-        <v>196</v>
+        <v>145</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0.2586</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="I111" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0.1939</v>
+        <v>0.5625</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Fall/Winter</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>36502</t>
+          <t>38501</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Blue Gingham Train Smocked Overalls</t>
+          <t>Blue Puppy Golf Shirt</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q23</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q2 ReOrder</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>46230</v>
+        <v>46221</v>
       </c>
       <c r="G112" t="n">
-        <v>100</v>
+        <v>238</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0.2275</v>
+        <v>0.1167</v>
       </c>
       <c r="I112" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0.4737</v>
+        <v>0.4286</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -6845,43 +6845,43 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>36506</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Brown Turkey Face Overalls</t>
+          <t>Green Tractor Golf Shirt</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q23</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q2 ReOrder</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>46230</v>
+        <v>46221</v>
       </c>
       <c r="G113" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>0.0798</v>
+        <v>0.064</v>
       </c>
       <c r="I113" t="n">
         <v>2</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>0.1333</v>
+        <v>0.125</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -6890,81 +6890,81 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>38074</t>
+          <t>70212</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Light Brown Turkey Shirt and Sage Green Pants Set</t>
+          <t>The Perfect Onesie Unisex Collared Romper</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q23</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q2 ReOrder</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>46230</v>
+        <v>46221</v>
       </c>
       <c r="G114" t="n">
-        <v>140</v>
+        <v>349</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0.1422</v>
+        <v>0.0692</v>
       </c>
       <c r="I114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0.1613</v>
+        <v>0.2222</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>38091</t>
+          <t>33281</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Light Gray Mallard Smocked Shirt and Pants</t>
+          <t>Pink Gingham ABC School Bishop Dress</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6974,32 +6974,32 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q34</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q3 New BtS &amp; Halloween</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>46230</v>
+        <v>46219</v>
       </c>
       <c r="G115" t="n">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.125</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7016,12 +7016,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>38097</t>
+          <t>33282</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>White Football Truck Shirt and Brown Pants Set</t>
+          <t>Blue Smocked Knit ABC School Dress</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7031,37 +7031,37 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q34</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q3 New BtS &amp; Halloween</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>46230</v>
+        <v>46219</v>
       </c>
       <c r="G116" t="n">
-        <v>62</v>
+        <v>204</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0.1034</v>
+        <v>0.1208</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0.0833</v>
+        <v>0</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Fall/Winter</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -7073,69 +7073,69 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>33283</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Light Blue Golf Hole Shirt</t>
+          <t>Pink and Orange GIngham Boo Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Stage 3</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q34</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q3 New BtS &amp; Halloween</t>
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>46230</v>
+        <v>46219</v>
       </c>
       <c r="G117" t="n">
-        <v>47</v>
+        <v>193</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>0</v>
+        <v>0.1458</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>0</v>
+        <v>0.0571</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Halloween</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>38505</t>
+          <t>33284</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sage Green Mallard Polo Shirt</t>
+          <t>Pink and Orange Gingham Boo Smocked Dress and Bloomer Set</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7145,28 +7145,28 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q34</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q3 New BtS &amp; Halloween</t>
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>46230</v>
+        <v>46219</v>
       </c>
       <c r="G118" t="n">
         <v>90</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.1429</v>
+        <v>0.175</v>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.0833</v>
+        <v>0.0476</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -7175,24 +7175,24 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Halloween</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>38517</t>
+          <t>36545</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Brown Turkey Face T-Shirt</t>
+          <t>Gray Boo Applique Overalls</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7202,22 +7202,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q34</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q3 New BtS &amp; Halloween</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>46230</v>
+        <v>46219</v>
       </c>
       <c r="G119" t="n">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>0.1271</v>
+        <v>0.1417</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Halloween</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -7244,12 +7244,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>38518</t>
+          <t>38125</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sand Beige Pumpkin Tractor Polo Golf Shirt</t>
+          <t>Blue Smocked ABC School Shirt and Shorts Set</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7259,37 +7259,37 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q34</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q3 New BtS &amp; Halloween</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>46230</v>
+        <v>46219</v>
       </c>
       <c r="G120" t="n">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0667</v>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Thanksgiving</t>
+          <t>Fall/Winter</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -7301,12 +7301,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>70214</t>
+          <t>38126</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>White Lace Collared Girls Long Sleeve Bodysuit Romper</t>
+          <t>Blue ABC School Shirt and Shorts Set</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7316,28 +7316,28 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q34</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q3 New BtS &amp; Halloween</t>
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>46230</v>
+        <v>46219</v>
       </c>
       <c r="G121" t="n">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0.0743</v>
+        <v>0.1167</v>
       </c>
       <c r="I121" t="n">
         <v>1</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -7346,24 +7346,24 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Fall/Winter</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>70226</t>
+          <t>38127</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>White Pointed Collar Button Romper</t>
+          <t>Gray Boo Applique Shirt and Pants Set</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7373,54 +7373,54 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>3LC26Q32</t>
+          <t>3LC26Q34</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FW26-B (Fall)</t>
+          <t>Q3 New BtS &amp; Halloween</t>
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>46230</v>
+        <v>46219</v>
       </c>
       <c r="G122" t="n">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>0.1111</v>
+        <v>0</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Halloween</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>33890</t>
+          <t>48922</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Light Blue Gingham Basic Baby Jon Jon</t>
+          <t>Grey Gingham Puppies in Truck Shortalls</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7430,28 +7430,28 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>4LC26Q22</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>Q2 restock</t>
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>46221</v>
+        <v>46211</v>
       </c>
       <c r="G123" t="n">
-        <v>266</v>
+        <v>66</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0.225</v>
+        <v>0.1053</v>
       </c>
       <c r="I123" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0.7531</v>
+        <v>0.5</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -7472,12 +7472,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>47894</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Green Gingham Alligator Bubble Romper</t>
+          <t>Light Blue Pumpkin Applique Collared Dress</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7487,28 +7487,28 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>4LC26Q32</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>FW26-B&amp;C</t>
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>46221</v>
+        <v>46204</v>
       </c>
       <c r="G124" t="n">
-        <v>263</v>
+        <v>133</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0.35</v>
+        <v>0.3599</v>
       </c>
       <c r="I124" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0.1948</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -7517,49 +7517,49 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>47901</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Light Blue Seersucker Ruffle Dress</t>
+          <t>Red Christmas Plaid Colllared Ruffle Dress</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Stage 2</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>4LC26Q32</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>FW26-B&amp;C</t>
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>46221</v>
+        <v>46204</v>
       </c>
       <c r="G125" t="n">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>0.3029</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
@@ -7574,138 +7574,138 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Christmas</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>48936</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>White and Blue Holy Smocked Overalls</t>
+          <t>Light Blue Pumpkin Applique Overalls</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Stage 2</t>
+          <t>Stage 1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>4LC26Q32</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>FW26-B&amp;C</t>
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>46221</v>
+        <v>46204</v>
       </c>
       <c r="G126" t="n">
-        <v>196</v>
+        <v>116</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0.1708</v>
+        <v>0.1429</v>
       </c>
       <c r="I126" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.0303</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Thanksgiving</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>36532</t>
+          <t>38516</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Blue Crosses Smocked JonJon</t>
+          <t>Sage Green Apple Polo Golf Shirt</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Stage 5</t>
+          <t>Stage 2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>3LC26Q31</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>FW26A BtS &amp; Halloween ReOrder</t>
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>46221</v>
+        <v>46188</v>
       </c>
       <c r="G127" t="n">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1533</v>
       </c>
       <c r="I127" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>0.5625</v>
+        <v>0</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>Fall/Winter</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Year-round</t>
+          <t>In season</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>38501</t>
+          <t>32089</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Blue Puppy Golf Shirt</t>
+          <t>Pink Gingham Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7715,28 +7715,28 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>3LC26Q21</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>Q2 Reorder</t>
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>46221</v>
+        <v>46168</v>
       </c>
       <c r="G128" t="n">
-        <v>238</v>
+        <v>146</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>0.1167</v>
+        <v>0.396</v>
       </c>
       <c r="I128" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>0.4286</v>
+        <v>0.5354</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -7757,47 +7757,47 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>38502</t>
+          <t>32553</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Green Tractor Golf Shirt</t>
+          <t>White and Pink Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Stage 3</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>3LC26Q21</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>Q2 Reorder</t>
         </is>
       </c>
       <c r="F129" s="2" t="n">
-        <v>46221</v>
+        <v>46168</v>
       </c>
       <c r="G129" t="n">
-        <v>217</v>
+        <v>152</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>0.064</v>
+        <v>0.1481</v>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>0.125</v>
+        <v>0.275</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -7814,47 +7814,47 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>70212</t>
+          <t>32556</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>The Perfect Onesie Unisex Collared Romper</t>
+          <t>Pink and White Smocked Bishop Dress</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Stage 1</t>
+          <t>Stage 0</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>3LC26Q23</t>
+          <t>3LC26Q21</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Q2 ReOrder</t>
+          <t>Q2 Reorder</t>
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>46221</v>
+        <v>46168</v>
       </c>
       <c r="G130" t="n">
-        <v>349</v>
+        <v>151</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>0.0692</v>
+        <v>0.3833</v>
       </c>
       <c r="I130" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>0.2222</v>
+        <v>0.1391</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -7871,157 +7871,157 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>33281</t>
+          <t>32572</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Pink Gingham ABC School Bishop Dress</t>
+          <t>Pink and White bows Smocked Ruffle Romper</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>3LC26Q34</t>
+          <t>3LC26Q21</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Q3 New BtS &amp; Halloween</t>
+          <t>Q2 Reorder</t>
         </is>
       </c>
       <c r="F131" s="2" t="n">
-        <v>46219</v>
+        <v>46168</v>
       </c>
       <c r="G131" t="n">
-        <v>206</v>
+        <v>104</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>0.125</v>
+        <v>0.3143</v>
       </c>
       <c r="I131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>0.2</v>
+        <v>0.0227</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Fall/Winter</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>33282</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Blue Smocked Knit ABC School Dress</t>
+          <t>Light Blue Crosses Smocked Overalls</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 2</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>3LC26Q34</t>
+          <t>3LC26Q21</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Q3 New BtS &amp; Halloween</t>
+          <t>Q2 Reorder</t>
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>46219</v>
+        <v>46168</v>
       </c>
       <c r="G132" t="n">
-        <v>204</v>
+        <v>264</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>0.1208</v>
+        <v>0.2722</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>0</v>
+        <v>0.1633</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Fall/Winter</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>33283</t>
+          <t>38504</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Pink and Orange GIngham Boo Smocked Bishop Dress</t>
+          <t>Light Blue Golf Hole Shirt</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>3LC26Q34</t>
+          <t>3LC26Q21</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Q3 New BtS &amp; Halloween</t>
+          <t>Q2 Reorder</t>
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>46219</v>
+        <v>46168</v>
       </c>
       <c r="G133" t="n">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>0.1458</v>
+        <v>0.2882</v>
       </c>
       <c r="I133" t="n">
         <v>2</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>0.0571</v>
+        <v>0.0408</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -8030,1100 +8030,74 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Halloween</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>In season</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>33284</t>
+          <t>70211</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Pink and Orange Gingham Boo Smocked Dress and Bloomer Set</t>
+          <t>White Organic Cotton Short Sleeve Bodysuit</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Stage 0</t>
+          <t>Stage 2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3LC26Q34</t>
+          <t>3LC26Q21</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Q3 New BtS &amp; Halloween</t>
+          <t>Q2 Reorder</t>
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>46219</v>
+        <v>46168</v>
       </c>
       <c r="G134" t="n">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0.175</v>
+        <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Halloween</t>
+          <t>Year-round</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>In season</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>36545</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Gray Boo Applique Overalls</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Stage 0</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3LC26Q34</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Q3 New BtS &amp; Halloween</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="G135" t="n">
-        <v>94</v>
-      </c>
-      <c r="H135" s="3" t="n">
-        <v>0.1417</v>
-      </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>Halloween</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>In season</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>38125</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Blue Smocked ABC School Shirt and Shorts Set</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Stage 0</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>3LC26Q34</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Q3 New BtS &amp; Halloween</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="G136" t="n">
-        <v>107</v>
-      </c>
-      <c r="H136" s="3" t="n">
-        <v>0.0667</v>
-      </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>Fall/Winter</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>In season</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>38126</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Blue ABC School Shirt and Shorts Set</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Stage 0</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>3LC26Q34</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Q3 New BtS &amp; Halloween</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="G137" t="n">
-        <v>110</v>
-      </c>
-      <c r="H137" s="3" t="n">
-        <v>0.1167</v>
-      </c>
-      <c r="I137" t="n">
-        <v>1</v>
-      </c>
-      <c r="J137" s="3" t="n">
-        <v>0.07140000000000001</v>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>Fall/Winter</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>In season</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>38127</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Gray Boo Applique Shirt and Pants Set</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Stage 0</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>3LC26Q34</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Q3 New BtS &amp; Halloween</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="G138" t="n">
-        <v>104</v>
-      </c>
-      <c r="H138" s="3" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>Halloween</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>In season</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>48922</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Grey Gingham Puppies in Truck Shortalls</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Stage 5</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>4LC26Q22</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Q2 restock</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>46211</v>
-      </c>
-      <c r="G139" t="n">
-        <v>66</v>
-      </c>
-      <c r="H139" s="3" t="n">
-        <v>0.1053</v>
-      </c>
-      <c r="I139" t="n">
-        <v>4</v>
-      </c>
-      <c r="J139" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
           <t>Year-round</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>47894</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Light Blue Pumpkin Applique Collared Dress</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Stage 1</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>4LC26Q32</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>FW26-B&amp;C</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="G140" t="n">
-        <v>133</v>
-      </c>
-      <c r="H140" s="3" t="n">
-        <v>0.3599</v>
-      </c>
-      <c r="I140" t="n">
-        <v>1</v>
-      </c>
-      <c r="J140" s="3" t="n">
-        <v>0.009599999999999999</v>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>Thanksgiving</t>
-        </is>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>In season</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>47901</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Red Christmas Plaid Colllared Ruffle Dress</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Stage 0</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>4LC26Q32</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>FW26-B&amp;C</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="G141" t="n">
-        <v>188</v>
-      </c>
-      <c r="H141" s="3" t="n">
-        <v>0.3029</v>
-      </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>Christmas</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>In season</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>48936</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Light Blue Pumpkin Applique Overalls</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Stage 1</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>4LC26Q32</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>FW26-B&amp;C</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>46204</v>
-      </c>
-      <c r="G142" t="n">
-        <v>116</v>
-      </c>
-      <c r="H142" s="3" t="n">
-        <v>0.1429</v>
-      </c>
-      <c r="I142" t="n">
-        <v>1</v>
-      </c>
-      <c r="J142" s="3" t="n">
-        <v>0.0303</v>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>Thanksgiving</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>In season</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>38516</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Sage Green Apple Polo Golf Shirt</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Stage 2</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>3LC26Q31</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>FW26A BtS &amp; Halloween ReOrder</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>46188</v>
-      </c>
-      <c r="G143" t="n">
-        <v>64</v>
-      </c>
-      <c r="H143" s="3" t="n">
-        <v>0.1533</v>
-      </c>
-      <c r="I143" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>Fall/Winter</t>
-        </is>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>In season</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>31893</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Red Gingham Barn Animals Smocked Bishop Dress</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Stage 0</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>3LC26Q21</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Q2 Reorder</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>46168</v>
-      </c>
-      <c r="G144" t="n">
-        <v>111</v>
-      </c>
-      <c r="H144" s="3" t="n">
-        <v>0.4895</v>
-      </c>
-      <c r="I144" t="n">
-        <v>39</v>
-      </c>
-      <c r="J144" s="3" t="n">
-        <v>0.4194</v>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>32089</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Pink Gingham Smocked Bishop Dress</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Stage 3</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>3LC26Q21</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Q2 Reorder</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>46168</v>
-      </c>
-      <c r="G145" t="n">
-        <v>146</v>
-      </c>
-      <c r="H145" s="3" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="I145" t="n">
-        <v>53</v>
-      </c>
-      <c r="J145" s="3" t="n">
-        <v>0.5354</v>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>32553</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>White and Pink Smocked Bishop Dress</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Stage 0</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>3LC26Q21</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Q2 Reorder</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>46168</v>
-      </c>
-      <c r="G146" t="n">
-        <v>152</v>
-      </c>
-      <c r="H146" s="3" t="n">
-        <v>0.1481</v>
-      </c>
-      <c r="I146" t="n">
-        <v>11</v>
-      </c>
-      <c r="J146" s="3" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>32556</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Pink and White Smocked Bishop Dress</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Stage 0</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3LC26Q21</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Q2 Reorder</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>46168</v>
-      </c>
-      <c r="G147" t="n">
-        <v>151</v>
-      </c>
-      <c r="H147" s="3" t="n">
-        <v>0.3833</v>
-      </c>
-      <c r="I147" t="n">
-        <v>16</v>
-      </c>
-      <c r="J147" s="3" t="n">
-        <v>0.1391</v>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>32570</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Pink and White Smocked Bubble Romper</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Stage 0</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>3LC26Q21</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Q2 Reorder</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>46168</v>
-      </c>
-      <c r="G148" t="n">
-        <v>71</v>
-      </c>
-      <c r="H148" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I148" t="n">
-        <v>9</v>
-      </c>
-      <c r="J148" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>32572</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Pink and White bows Smocked Ruffle Romper</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Stage 3</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>3LC26Q21</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Q2 Reorder</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>46168</v>
-      </c>
-      <c r="G149" t="n">
-        <v>104</v>
-      </c>
-      <c r="H149" s="3" t="n">
-        <v>0.3143</v>
-      </c>
-      <c r="I149" t="n">
-        <v>1</v>
-      </c>
-      <c r="J149" s="3" t="n">
-        <v>0.0227</v>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>36366</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Light Blue Crosses Smocked Overalls</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Stage 2</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>3LC26Q21</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Q2 Reorder</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>46168</v>
-      </c>
-      <c r="G150" t="n">
-        <v>264</v>
-      </c>
-      <c r="H150" s="3" t="n">
-        <v>0.2722</v>
-      </c>
-      <c r="I150" t="n">
-        <v>8</v>
-      </c>
-      <c r="J150" s="3" t="n">
-        <v>0.1633</v>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>38504</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Light Blue Golf Hole Shirt</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Stage 3</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>3LC26Q21</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Q2 Reorder</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="n">
-        <v>46168</v>
-      </c>
-      <c r="G151" t="n">
-        <v>96</v>
-      </c>
-      <c r="H151" s="3" t="n">
-        <v>0.2882</v>
-      </c>
-      <c r="I151" t="n">
-        <v>2</v>
-      </c>
-      <c r="J151" s="3" t="n">
-        <v>0.0408</v>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>70211</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>White Organic Cotton Short Sleeve Bodysuit</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Stage 2</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3LC26Q21</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Q2 Reorder</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>46168</v>
-      </c>
-      <c r="G152" t="n">
-        <v>147</v>
-      </c>
-      <c r="H152" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M152"/>
+  <autoFilter ref="A1:M134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>